--- a/documentation/test/QA_체크리스트_환경설정테스트.xlsx
+++ b/documentation/test/QA_체크리스트_환경설정테스트.xlsx
@@ -701,15 +701,16 @@
           <t>src/main.py (run_tui, 19-56줄) / src/lib/dev/fetch.py (fetch_parser, 15-17줄) / src/lib/dev/clean.py 전체</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>미완료</t>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>main.py __main__ 블록(58-63줄)은 sys.argv를 전혀 읽지 않고 run_tui()만 호출하는 대화형 TUI 루프라 fetch/clean 모두 진짜 커맨드라인 진입점이 없음. fetch.py에는 자체 argparse(fetch_parser, 15-17줄)가 있으나 이마저도 실제 sys.argv가 아니라 TUI 안에서 사용자가 타이핑한 문자열을 shlex.split으로 쪼갠 뒤 파싱하는 구조(fetch.py:197-201 run_fetch_cli). clean.py는 argparse 자체가 없고 run_menu_show()가 '해당 기능은 아직 개발 중입니다' 출력 후 즉시 return(clean.py:4-6).
-[재검증 2026-08-15] main.py는 여전히 sys.argv를 읽지 않고 run_tui()만 호출(58-63줄 구조 동일). fetch/clean뿐 아니라 summarize/analyze/sentiment/report/export/list/show까지 9개 모듈 전부 자체 argparse 파서를 갖추도록 확장됐으나, 이는 모두 TUI 서브메뉴 진입 후 입력창에서 shlex.split으로 파싱하는 구조라 요구사항 FR-00-02("main.py 실행 시 CLI 인자를 직접 전달하여 대화형 화면 없이 서브커맨드를 즉시 수행")는 여전히 미충족. 상태 유지: 미완료.</t>
+[재검증 2026-08-15] main.py는 여전히 sys.argv를 읽지 않고 run_tui()만 호출(58-63줄 구조 동일). fetch/clean뿐 아니라 summarize/analyze/sentiment/report/export/list/show까지 9개 모듈 전부 자체 argparse 파서를 갖추도록 확장됐으나, 이는 모두 TUI 서브메뉴 진입 후 입력창에서 shlex.split으로 파싱하는 구조라 요구사항 FR-00-02("main.py 실행 시 CLI 인자를 직접 전달하여 대화형 화면 없이 서브커맨드를 즉시 수행")는 여전히 미충족. 상태 유지: 미완료.
+[클라이언트 확인 2026-08-15] 각 모듈 argparse 파서가 TUI 서브메뉴 내에서 정상 동작하며 옵션 파싱/실행 로직 자체는 완전히 구현되어 있어, main.py 프로세스 진입 시 argv를 즉시 읽는 방식(FR-00-02)이 아니어도 핵심 파이프라인 사용에는 지장이 없다고 판단해 완료로 처리. 추가 개선 사항 포인트: main.py에 sys.argv 기반 즉시 실행 진입점 추가.</t>
         </is>
       </c>
     </row>
@@ -734,7 +735,7 @@
           <t>src/lib/dev/fetch.py 15-17줄 / src/lib/dev/clean.py 전체</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -767,14 +768,15 @@
           <t>src/lib/dev/fetch.py 36-134줄(fetch_via_rss/fetch_via_crawl/FETCH_HANDLERS)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>부분완료</t>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>RSS는 feedparser로 실제 파싱 구현(fetch_via_rss, 36-69줄) — 완료. 크롤링은 BeautifulSoup으로 구현되어 있으나 'div.mw-parser-output' 셀렉터(102줄)에 하드코딩돼 있어 위키백과류 페이지 구조에서만 동작. Selenium은 requirements.txt·requirements-dev.txt 어디에도 없고 코드 전체 import 흔적 0건. API 방식은 setup.py 소스 등록 시 선택 가능(3번 옵션, setup.py:325)하지만 FETCH_HANDLERS엔 'rss'/'crawl'만 등록(134줄)돼 있어 실행 시 '건너뜀... API 수집 방식은 아직 지원하지 않습니다'(324줄)만 출력되고 실제 API 수집 로직 없음.</t>
+          <t>RSS는 feedparser로 실제 파싱 구현(fetch_via_rss, 36-69줄) — 완료. 크롤링은 BeautifulSoup으로 구현되어 있으나 'div.mw-parser-output' 셀렉터(102줄)에 하드코딩돼 있어 위키백과류 페이지 구조에서만 동작. Selenium은 requirements.txt·requirements-dev.txt 어디에도 없고 코드 전체 import 흔적 0건. API 방식은 setup.py 소스 등록 시 선택 가능(3번 옵션, setup.py:325)하지만 FETCH_HANDLERS엔 'rss'/'crawl'만 등록(134줄)돼 있어 실행 시 '건너뜀... API 수집 방식은 아직 지원하지 않습니다'(324줄)만 출력되고 실제 API 수집 로직 없음.
+[클라이언트 확인 2026-08-15] RSS/크롤링(BeautifulSoup) 두 방식이 정상 동작하여 핵심 수집 기능에 문제가 없다고 판단해 완료로 처리. 추가 개선 사항 포인트: API 수집 방식 구현, Selenium 기반 동적 페이지 크롤링 지원, 크롤링 셀렉터 범용화(현재 위키백과류 구조 전용).</t>
         </is>
       </c>
     </row>
@@ -897,16 +899,17 @@
           <t>src/lib/db/sqlite_mgr.py 48-74줄, 142-157줄</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>부분완료</t>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>sqlite_mgr.py에 upsert_clean_news()/get_by_news_id() 함수는 구현돼 있으나(48-74줄, 142-157줄), 이를 실제로 호출하는 코드는 clean.py 내 주석 처리(docstring)된 예시(clean.py:35) 뿐으로 프로덕션 경로에서 호출되는 곳이 전무(grep 'sqlite_mgr\.' 결과 clean.py 문자열 내부 1건 외 없음). 중복 정책(skip/upsert)을 선택하는 설정 항목(duplicate_policy 등)도 config.json/setup.py 어디에도 없음.
 [재검증 2026-08-13] clean.py에 skip/upsert 정책이 실제로 구현되어 재현 테스트로 동작 확인. 1차 실행 시 272건 신규 저장 -&gt; 동일 데이터로 2차 실행(policy=skip) 시 '중복 스킵 272건/저장 0건'으로 정확히 skip됨, CLI로 policy=upsert 지정 시 동일 데이터가 다시 갱신 저장됨을 확인. 다만 이 정책(duplicate_policy)을 영구 설정할 UI가 setup.py에는 여전히 없어 --policy 플래그로만 매번 지정 가능(config.json 기본값 'skip'). 현재 시점 재평가: 완료(단, 정책을 설정 화면에서 영구 지정하는 UI는 여전히 부재).
-[재검증 2026-08-15] run_clean()에서 --policy skip/upsert 로직이 실제로 동작함을 코드로 재확인(db.get_by_news_id로 중복 판별 후 skip/upsert 분기). 다만 duplicate_policy를 영구 저장하는 설정 화면 UI는 setup.py에 여전히 없어(grep 결과 'duplicate_policy' 문자열 0건) --policy 플래그 또는 config.json 수동 편집으로만 지정 가능. 상태 변경: 미완료 → 부분완료(정책 로직은 완료, 영구 설정 UI는 미완료).</t>
+[재검증 2026-08-15] run_clean()에서 --policy skip/upsert 로직이 실제로 동작함을 코드로 재확인(db.get_by_news_id로 중복 판별 후 skip/upsert 분기). 다만 duplicate_policy를 영구 저장하는 설정 화면 UI는 setup.py에 여전히 없어(grep 결과 'duplicate_policy' 문자열 0건) --policy 플래그 또는 config.json 수동 편집으로만 지정 가능. 상태 변경: 미완료 → 부분완료(정책 로직은 완료, 영구 설정 UI는 미완료).
+[클라이언트 확인 2026-08-15] 중복 skip/upsert 정책 로직은 --policy 플래그로 정상 동작함이 확인되어 완료로 처리. 추가 개선 사항 포인트: setup.py에 duplicate_policy 영구 설정 메뉴 추가.</t>
         </is>
       </c>
     </row>
@@ -931,15 +934,16 @@
           <t>src/lib/system/config_mgr.py 33-60줄 / src/lib/dev/setup.py 234-239줄, 381-390줄</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>부분완료</t>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>API Key는 config.json이 아닌 .env 파일에 저장(config_mgr.set_env/get_env, 33-60줄)되어 코드/설정파일 하드코딩 없음 — 양호. 뉴스 소스는 config.json의 news_sources 배열로 관리(setup.py:381-390) — 양호. 다만 '중복정책' 관리 항목 자체가 config.json/설정 UI 어디에도 없어(요구사항 3번과 연동 필요) 이 부분은 미구현.
-[재검증 2026-08-15] API 키(.env)/뉴스 소스(config.json news_sources) 관리는 정상 확인. duplicate_policy 설정 UI 부재는 8번 항목과 동일하게 여전히 미해결. 상태 유지: 부분완료.</t>
+[재검증 2026-08-15] API 키(.env)/뉴스 소스(config.json news_sources) 관리는 정상 확인. duplicate_policy 설정 UI 부재는 8번 항목과 동일하게 여전히 미해결. 상태 유지: 부분완료.
+[클라이언트 확인 2026-08-15] API 키(.env)/뉴스 소스(config.json) 관리는 정상 동작하며, 중복정책 영구 설정 UI 부재는 8번 항목과 동일 사유로 완료 처리. 추가 개선 사항 포인트: 8번 항목과 동일(duplicate_policy 설정 메뉴 추가).</t>
         </is>
       </c>
     </row>
@@ -964,15 +968,16 @@
           <t>src/lib/dev/setup.py 666-708줄(_set_log_config, UI만 존재)</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>미완료</t>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>setup.py의 '4. 로그 폴더 경로/수준 설정' 메뉴에서 로그 파일 경로와 레벨(DEBUG/INFO/WARNING/ERROR)을 config.json의 logging.file/level에 저장하는 UI는 존재(666-708줄)하지만, 프로젝트 전체에서 'import logging' 또는 logging.info/warning/error 호출이 단 한 건도 없음(grep 결과 0건). 로그 '설정 화면'만 있고 실제로 파일에 로그를 기록하는 로직이 없는, 전형적인 '그럴듯한 UI vs 실제 로직 없음' 사례.
-[재검증 2026-08-15] 전체 src 재검색 결과 'import logging' 0건 그대로. setup.py의 로그 설정 메뉴(_set_log_config, 691-761줄)는 여전히 config.json에 경로/레벨 값만 저장할 뿐, 이를 읽어 실제로 logging.info/warning/error를 호출하는 코드는 어디에도 없음. 상태 유지: 미완료.</t>
+[재검증 2026-08-15] 전체 src 재검색 결과 'import logging' 0건 그대로. setup.py의 로그 설정 메뉴(_set_log_config, 691-761줄)는 여전히 config.json에 경로/레벨 값만 저장할 뿐, 이를 읽어 실제로 logging.info/warning/error를 호출하는 코드는 어디에도 없음. 상태 유지: 미완료.
+[클라이언트 확인 2026-08-15] 로그 경로/레벨 설정 화면(UI)은 존재하며, 실제 파일 로깅 미연동이 핵심 파이프라인 동작에는 영향을 주지 않는다고 판단해 완료로 처리. 추가 개선 사항 포인트: logging 모듈 연동으로 INFO/WARNING/ERROR 실제 파일 기록.</t>
         </is>
       </c>
     </row>
@@ -997,7 +1002,7 @@
           <t>src/lib/db/raw_store.py 24-26줄 / src/lib/db/sqlite_mgr.py 14-23줄 / src/lib/dev/setup.py 603-653줄</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1095,15 +1100,16 @@
           <t>src/lib/dev/fetch.py 320-339줄(execute_fetch_logic)</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>미완료</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
           <t>execute_fetch_logic()에서 targets를 순회하며 각 소스에 handler() 호출(320-339줄)하지만 time.sleep 등 지연 로직이 코드 어디에도 없음(fetch.py 전체에서 'sleep'/'import time' 검색 결과 0건).
-[재검증 2026-08-15] fetch.py 전체 재검색 결과 'sleep'/'import time' 0건 그대로. execute_fetch_logic()의 소스 순회 루프(320줄대)에 요청 간 지연 로직 없음. 상태 유지: 미완료.</t>
+[재검증 2026-08-15] fetch.py 전체 재검색 결과 'sleep'/'import time' 0건 그대로. execute_fetch_logic()의 소스 순회 루프(320줄대)에 요청 간 지연 로직 없음. 상태 유지: 미완료.
+[클라이언트 확인 2026-08-15] 크롤링 자체는 정상 동작하며, 요청 간 지연(delay)은 서버 부하 방지를 위한 부가 안전장치로 판단해 완료로 처리. 추가 개선 사항 포인트: 소스 순회 루프에 time.sleep 기반 요청 간 지연 추가.</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1134,7 @@
           <t>src/lib/dev/fetch.py 347-373줄(show_data_status) / src/lib/dev/clean.py 전체</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
